--- a/WVS_Dataset/Codebook manual coded index.xlsx
+++ b/WVS_Dataset/Codebook manual coded index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa349\Dropbox\Teaching\2024 PSYC 382 Culture and Cognition\Lab Shiny Server\WVS7_Shiny_App\WVS_Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Blob\Documents\GitHub\WorldView\WVS_Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8A2FC4-E4B5-41C6-BAB5-E9FE17AA633F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C2D07-F5F2-4F7E-92CC-8F053A43FFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12040" yWindow="7080" windowWidth="25830" windowHeight="22640" xr2:uid="{1F33E572-B13C-43FB-A92D-13F49A1A14C4}"/>
+    <workbookView xWindow="-5685" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{1F33E572-B13C-43FB-A92D-13F49A1A14C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2897,7 +2897,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3228,18 +3239,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5699022E-E034-4B52-8E71-081D69E78013}">
   <dimension ref="A1:H300"/>
-  <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
-    <col min="3" max="3" width="70.54296875" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="22.54296875" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" customWidth="1"/>
+    <col min="3" max="3" width="70.5546875" customWidth="1"/>
+    <col min="4" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3265,7 +3276,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>922</v>
       </c>
@@ -3282,7 +3293,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>932</v>
       </c>
@@ -3299,7 +3310,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>923</v>
       </c>
@@ -3316,7 +3327,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3336,10 +3347,10 @@
         <v>446</v>
       </c>
       <c r="H5" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3359,10 +3370,10 @@
         <v>446</v>
       </c>
       <c r="H6" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3382,10 +3393,10 @@
         <v>446</v>
       </c>
       <c r="H7" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3405,10 +3416,10 @@
         <v>446</v>
       </c>
       <c r="H8" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -3428,10 +3439,10 @@
         <v>446</v>
       </c>
       <c r="H9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -3451,10 +3462,10 @@
         <v>446</v>
       </c>
       <c r="H10" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3474,10 +3485,10 @@
         <v>446</v>
       </c>
       <c r="H11" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3497,10 +3508,10 @@
         <v>446</v>
       </c>
       <c r="H12" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3520,10 +3531,10 @@
         <v>446</v>
       </c>
       <c r="H13" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3543,10 +3554,10 @@
         <v>446</v>
       </c>
       <c r="H14" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -3566,10 +3577,10 @@
         <v>446</v>
       </c>
       <c r="H15" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3589,10 +3600,10 @@
         <v>446</v>
       </c>
       <c r="H16" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3612,10 +3623,10 @@
         <v>446</v>
       </c>
       <c r="H17" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -3635,10 +3646,10 @@
         <v>446</v>
       </c>
       <c r="H18" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3658,10 +3669,10 @@
         <v>446</v>
       </c>
       <c r="H19" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3681,10 +3692,10 @@
         <v>446</v>
       </c>
       <c r="H20" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3704,10 +3715,10 @@
         <v>446</v>
       </c>
       <c r="H21" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -3727,10 +3738,10 @@
         <v>446</v>
       </c>
       <c r="H22" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -3750,10 +3761,10 @@
         <v>446</v>
       </c>
       <c r="H23" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3773,10 +3784,10 @@
         <v>446</v>
       </c>
       <c r="H24" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -3796,10 +3807,10 @@
         <v>446</v>
       </c>
       <c r="H25" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -3819,10 +3830,10 @@
         <v>446</v>
       </c>
       <c r="H26" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -3842,10 +3853,10 @@
         <v>446</v>
       </c>
       <c r="H27" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -3865,10 +3876,10 @@
         <v>446</v>
       </c>
       <c r="H28" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -3888,10 +3899,10 @@
         <v>446</v>
       </c>
       <c r="H29" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -3911,10 +3922,10 @@
         <v>446</v>
       </c>
       <c r="H30" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -3934,10 +3945,10 @@
         <v>446</v>
       </c>
       <c r="H31" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -3957,10 +3968,10 @@
         <v>446</v>
       </c>
       <c r="H32" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -3980,10 +3991,10 @@
         <v>446</v>
       </c>
       <c r="H33" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -4003,10 +4014,10 @@
         <v>446</v>
       </c>
       <c r="H34" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -4026,10 +4037,10 @@
         <v>446</v>
       </c>
       <c r="H35" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -4049,10 +4060,10 @@
         <v>446</v>
       </c>
       <c r="H36" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -4072,10 +4083,10 @@
         <v>446</v>
       </c>
       <c r="H37" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -4095,10 +4106,10 @@
         <v>446</v>
       </c>
       <c r="H38" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -4118,10 +4129,10 @@
         <v>446</v>
       </c>
       <c r="H39" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -4141,10 +4152,10 @@
         <v>446</v>
       </c>
       <c r="H40" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -4164,10 +4175,10 @@
         <v>446</v>
       </c>
       <c r="H41" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -4187,10 +4198,10 @@
         <v>446</v>
       </c>
       <c r="H42" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -4210,10 +4221,10 @@
         <v>446</v>
       </c>
       <c r="H43" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -4233,10 +4244,10 @@
         <v>446</v>
       </c>
       <c r="H44" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -4256,10 +4267,10 @@
         <v>446</v>
       </c>
       <c r="H45" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -4276,10 +4287,10 @@
         <v>446</v>
       </c>
       <c r="H46" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -4299,10 +4310,10 @@
         <v>446</v>
       </c>
       <c r="H47" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -4322,10 +4333,10 @@
         <v>446</v>
       </c>
       <c r="H48" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -4345,10 +4356,10 @@
         <v>446</v>
       </c>
       <c r="H49" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -4365,10 +4376,10 @@
         <v>446</v>
       </c>
       <c r="H50" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -4385,10 +4396,10 @@
         <v>446</v>
       </c>
       <c r="H51" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -4408,10 +4419,10 @@
         <v>452</v>
       </c>
       <c r="H52" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -4431,10 +4442,10 @@
         <v>452</v>
       </c>
       <c r="H53" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -4454,10 +4465,10 @@
         <v>452</v>
       </c>
       <c r="H54" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -4477,10 +4488,10 @@
         <v>446</v>
       </c>
       <c r="H55" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -4500,10 +4511,10 @@
         <v>446</v>
       </c>
       <c r="H56" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>446</v>
       </c>
       <c r="H57" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -4546,10 +4557,10 @@
         <v>446</v>
       </c>
       <c r="H58" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -4569,10 +4580,10 @@
         <v>446</v>
       </c>
       <c r="H59" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -4589,10 +4600,10 @@
         <v>928</v>
       </c>
       <c r="H60" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -4609,10 +4620,10 @@
         <v>928</v>
       </c>
       <c r="H61" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -4632,10 +4643,10 @@
         <v>446</v>
       </c>
       <c r="H62" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -4655,10 +4666,10 @@
         <v>446</v>
       </c>
       <c r="H63" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -4678,10 +4689,10 @@
         <v>446</v>
       </c>
       <c r="H64" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -4701,10 +4712,10 @@
         <v>446</v>
       </c>
       <c r="H65" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -4724,10 +4735,10 @@
         <v>446</v>
       </c>
       <c r="H66" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -4747,10 +4758,10 @@
         <v>446</v>
       </c>
       <c r="H67" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -4773,10 +4784,10 @@
         <v>446</v>
       </c>
       <c r="H68" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -4796,10 +4807,10 @@
         <v>446</v>
       </c>
       <c r="H69" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -4819,10 +4830,10 @@
         <v>446</v>
       </c>
       <c r="H70" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -4842,10 +4853,10 @@
         <v>446</v>
       </c>
       <c r="H71" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -4865,10 +4876,10 @@
         <v>446</v>
       </c>
       <c r="H72" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -4888,10 +4899,10 @@
         <v>446</v>
       </c>
       <c r="H73" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -4911,10 +4922,10 @@
         <v>446</v>
       </c>
       <c r="H74" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -4934,10 +4945,10 @@
         <v>446</v>
       </c>
       <c r="H75" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -4957,10 +4968,10 @@
         <v>446</v>
       </c>
       <c r="H76" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -4980,10 +4991,10 @@
         <v>446</v>
       </c>
       <c r="H77" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -5003,10 +5014,10 @@
         <v>446</v>
       </c>
       <c r="H78" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -5026,10 +5037,10 @@
         <v>446</v>
       </c>
       <c r="H79" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -5049,10 +5060,10 @@
         <v>446</v>
       </c>
       <c r="H80" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -5072,10 +5083,10 @@
         <v>446</v>
       </c>
       <c r="H81" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -5095,10 +5106,10 @@
         <v>446</v>
       </c>
       <c r="H82" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -5118,10 +5129,10 @@
         <v>446</v>
       </c>
       <c r="H83" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -5141,10 +5152,10 @@
         <v>446</v>
       </c>
       <c r="H84" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -5164,10 +5175,10 @@
         <v>446</v>
       </c>
       <c r="H85" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -5190,10 +5201,10 @@
         <v>446</v>
       </c>
       <c r="H86" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -5213,10 +5224,10 @@
         <v>446</v>
       </c>
       <c r="H87" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -5236,10 +5247,10 @@
         <v>446</v>
       </c>
       <c r="H88" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -5259,10 +5270,10 @@
         <v>446</v>
       </c>
       <c r="H89" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -5282,10 +5293,10 @@
         <v>446</v>
       </c>
       <c r="H90" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -5305,10 +5316,10 @@
         <v>446</v>
       </c>
       <c r="H91" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -5328,10 +5339,10 @@
         <v>446</v>
       </c>
       <c r="H92" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -5351,10 +5362,10 @@
         <v>446</v>
       </c>
       <c r="H93" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -5377,10 +5388,10 @@
         <v>452</v>
       </c>
       <c r="H94" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -5400,10 +5411,10 @@
         <v>928</v>
       </c>
       <c r="H95" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -5423,10 +5434,10 @@
         <v>928</v>
       </c>
       <c r="H96" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -5446,10 +5457,10 @@
         <v>928</v>
       </c>
       <c r="H97" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -5469,10 +5480,10 @@
         <v>928</v>
       </c>
       <c r="H98" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -5492,10 +5503,10 @@
         <v>928</v>
       </c>
       <c r="H99" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -5515,10 +5526,10 @@
         <v>928</v>
       </c>
       <c r="H100" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -5538,10 +5549,10 @@
         <v>928</v>
       </c>
       <c r="H101" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -5561,10 +5572,10 @@
         <v>928</v>
       </c>
       <c r="H102" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -5584,10 +5595,10 @@
         <v>928</v>
       </c>
       <c r="H103" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -5607,10 +5618,10 @@
         <v>928</v>
       </c>
       <c r="H104" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -5630,10 +5641,10 @@
         <v>928</v>
       </c>
       <c r="H105" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -5653,10 +5664,10 @@
         <v>928</v>
       </c>
       <c r="H106" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -5676,10 +5687,10 @@
         <v>928</v>
       </c>
       <c r="H107" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -5699,10 +5710,10 @@
         <v>928</v>
       </c>
       <c r="H108" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -5722,10 +5733,10 @@
         <v>928</v>
       </c>
       <c r="H109" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -5748,10 +5759,10 @@
         <v>452</v>
       </c>
       <c r="H110" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -5774,10 +5785,10 @@
         <v>452</v>
       </c>
       <c r="H111" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -5800,10 +5811,10 @@
         <v>452</v>
       </c>
       <c r="H112" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -5826,10 +5837,10 @@
         <v>452</v>
       </c>
       <c r="H113" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -5852,10 +5863,10 @@
         <v>452</v>
       </c>
       <c r="H114" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -5878,10 +5889,10 @@
         <v>928</v>
       </c>
       <c r="H115" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -5904,10 +5915,10 @@
         <v>452</v>
       </c>
       <c r="H116" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -5927,10 +5938,10 @@
         <v>446</v>
       </c>
       <c r="H117" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -5950,10 +5961,10 @@
         <v>446</v>
       </c>
       <c r="H118" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -5973,10 +5984,10 @@
         <v>446</v>
       </c>
       <c r="H119" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -5996,10 +6007,10 @@
         <v>446</v>
       </c>
       <c r="H120" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -6019,10 +6030,10 @@
         <v>446</v>
       </c>
       <c r="H121" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -6039,10 +6050,10 @@
         <v>446</v>
       </c>
       <c r="H122" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -6059,10 +6070,10 @@
         <v>446</v>
       </c>
       <c r="H123" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -6082,10 +6093,10 @@
         <v>446</v>
       </c>
       <c r="H124" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -6102,10 +6113,10 @@
         <v>446</v>
       </c>
       <c r="H125" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -6125,10 +6136,10 @@
         <v>446</v>
       </c>
       <c r="H126" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -6148,10 +6159,10 @@
         <v>446</v>
       </c>
       <c r="H127" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -6171,10 +6182,10 @@
         <v>446</v>
       </c>
       <c r="H128" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -6194,10 +6205,10 @@
         <v>446</v>
       </c>
       <c r="H129" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -6217,10 +6228,10 @@
         <v>446</v>
       </c>
       <c r="H130" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -6240,10 +6251,10 @@
         <v>446</v>
       </c>
       <c r="H131" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -6263,10 +6274,10 @@
         <v>446</v>
       </c>
       <c r="H132" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -6286,10 +6297,10 @@
         <v>446</v>
       </c>
       <c r="H133" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -6306,10 +6317,10 @@
         <v>446</v>
       </c>
       <c r="H134" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -6326,10 +6337,10 @@
         <v>446</v>
       </c>
       <c r="H135" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -6349,10 +6360,10 @@
         <v>446</v>
       </c>
       <c r="H136" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -6372,10 +6383,10 @@
         <v>446</v>
       </c>
       <c r="H137" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -6395,10 +6406,10 @@
         <v>446</v>
       </c>
       <c r="H138" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -6418,10 +6429,10 @@
         <v>446</v>
       </c>
       <c r="H139" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -6441,10 +6452,10 @@
         <v>446</v>
       </c>
       <c r="H140" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -6464,10 +6475,10 @@
         <v>446</v>
       </c>
       <c r="H141" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -6487,10 +6498,10 @@
         <v>446</v>
       </c>
       <c r="H142" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -6510,10 +6521,10 @@
         <v>928</v>
       </c>
       <c r="H143" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -6533,10 +6544,10 @@
         <v>928</v>
       </c>
       <c r="H144" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -6556,10 +6567,10 @@
         <v>928</v>
       </c>
       <c r="H145" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -6579,10 +6590,10 @@
         <v>446</v>
       </c>
       <c r="H146" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -6602,10 +6613,10 @@
         <v>446</v>
       </c>
       <c r="H147" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -6625,10 +6636,10 @@
         <v>928</v>
       </c>
       <c r="H148" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -6648,10 +6659,10 @@
         <v>928</v>
       </c>
       <c r="H149" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -6671,10 +6682,10 @@
         <v>446</v>
       </c>
       <c r="H150" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -6694,10 +6705,10 @@
         <v>446</v>
       </c>
       <c r="H151" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -6717,10 +6728,10 @@
         <v>446</v>
       </c>
       <c r="H152" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -6737,10 +6748,10 @@
         <v>928</v>
       </c>
       <c r="H153" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -6757,10 +6768,10 @@
         <v>928</v>
       </c>
       <c r="H154" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -6777,10 +6788,10 @@
         <v>928</v>
       </c>
       <c r="H155" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -6800,10 +6811,10 @@
         <v>928</v>
       </c>
       <c r="H156" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -6823,10 +6834,10 @@
         <v>928</v>
       </c>
       <c r="H157" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -6843,10 +6854,10 @@
         <v>928</v>
       </c>
       <c r="H158" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -6863,10 +6874,10 @@
         <v>928</v>
       </c>
       <c r="H159" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -6883,10 +6894,10 @@
         <v>928</v>
       </c>
       <c r="H160" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -6903,10 +6914,10 @@
         <v>928</v>
       </c>
       <c r="H161" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -6929,10 +6940,10 @@
         <v>452</v>
       </c>
       <c r="H162" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -6955,10 +6966,10 @@
         <v>452</v>
       </c>
       <c r="H163" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -6981,10 +6992,10 @@
         <v>452</v>
       </c>
       <c r="H164" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -7007,10 +7018,10 @@
         <v>452</v>
       </c>
       <c r="H165" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -7033,10 +7044,10 @@
         <v>452</v>
       </c>
       <c r="H166" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -7056,10 +7067,10 @@
         <v>452</v>
       </c>
       <c r="H167" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>196</v>
       </c>
@@ -7079,10 +7090,10 @@
         <v>452</v>
       </c>
       <c r="H168" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>197</v>
       </c>
@@ -7102,10 +7113,10 @@
         <v>928</v>
       </c>
       <c r="H169" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>198</v>
       </c>
@@ -7125,10 +7136,10 @@
         <v>928</v>
       </c>
       <c r="H170" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -7151,7 +7162,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>200</v>
       </c>
@@ -7171,10 +7182,10 @@
         <v>928</v>
       </c>
       <c r="H172" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>201</v>
       </c>
@@ -7194,10 +7205,10 @@
         <v>446</v>
       </c>
       <c r="H173" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>202</v>
       </c>
@@ -7217,10 +7228,10 @@
         <v>446</v>
       </c>
       <c r="H174" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>203</v>
       </c>
@@ -7237,10 +7248,10 @@
         <v>446</v>
       </c>
       <c r="H175" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>204</v>
       </c>
@@ -7257,10 +7268,10 @@
         <v>446</v>
       </c>
       <c r="H176" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>205</v>
       </c>
@@ -7277,10 +7288,10 @@
         <v>928</v>
       </c>
       <c r="H177" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>206</v>
       </c>
@@ -7297,10 +7308,10 @@
         <v>928</v>
       </c>
       <c r="H178" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>207</v>
       </c>
@@ -7317,10 +7328,10 @@
         <v>928</v>
       </c>
       <c r="H179" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>208</v>
       </c>
@@ -7340,10 +7351,10 @@
         <v>452</v>
       </c>
       <c r="H180" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>209</v>
       </c>
@@ -7369,7 +7380,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>210</v>
       </c>
@@ -7395,7 +7406,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>211</v>
       </c>
@@ -7421,7 +7432,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>212</v>
       </c>
@@ -7447,7 +7458,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>213</v>
       </c>
@@ -7473,7 +7484,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>214</v>
       </c>
@@ -7499,7 +7510,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>215</v>
       </c>
@@ -7525,7 +7536,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>216</v>
       </c>
@@ -7551,7 +7562,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>217</v>
       </c>
@@ -7577,7 +7588,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>218</v>
       </c>
@@ -7603,7 +7614,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>219</v>
       </c>
@@ -7629,7 +7640,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>220</v>
       </c>
@@ -7655,7 +7666,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>221</v>
       </c>
@@ -7681,7 +7692,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>222</v>
       </c>
@@ -7707,7 +7718,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>223</v>
       </c>
@@ -7733,7 +7744,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>224</v>
       </c>
@@ -7759,7 +7770,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>225</v>
       </c>
@@ -7785,7 +7796,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>226</v>
       </c>
@@ -7811,7 +7822,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>227</v>
       </c>
@@ -7837,7 +7848,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>228</v>
       </c>
@@ -7857,10 +7868,10 @@
         <v>446</v>
       </c>
       <c r="H200" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>229</v>
       </c>
@@ -7880,10 +7891,10 @@
         <v>446</v>
       </c>
       <c r="H201" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>230</v>
       </c>
@@ -7903,10 +7914,10 @@
         <v>446</v>
       </c>
       <c r="H202" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>231</v>
       </c>
@@ -7923,10 +7934,10 @@
         <v>446</v>
       </c>
       <c r="H203" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>232</v>
       </c>
@@ -7943,10 +7954,10 @@
         <v>446</v>
       </c>
       <c r="H204" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>233</v>
       </c>
@@ -7966,10 +7977,10 @@
         <v>446</v>
       </c>
       <c r="H205" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>234</v>
       </c>
@@ -7989,10 +8000,10 @@
         <v>446</v>
       </c>
       <c r="H206" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>235</v>
       </c>
@@ -8012,10 +8023,10 @@
         <v>446</v>
       </c>
       <c r="H207" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>236</v>
       </c>
@@ -8035,10 +8046,10 @@
         <v>446</v>
       </c>
       <c r="H208" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>237</v>
       </c>
@@ -8058,10 +8069,10 @@
         <v>446</v>
       </c>
       <c r="H209" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>238</v>
       </c>
@@ -8081,10 +8092,10 @@
         <v>446</v>
       </c>
       <c r="H210" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>239</v>
       </c>
@@ -8104,10 +8115,10 @@
         <v>446</v>
       </c>
       <c r="H211" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>240</v>
       </c>
@@ -8127,10 +8138,10 @@
         <v>446</v>
       </c>
       <c r="H212" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>241</v>
       </c>
@@ -8150,10 +8161,10 @@
         <v>446</v>
       </c>
       <c r="H213" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>242</v>
       </c>
@@ -8173,10 +8184,10 @@
         <v>446</v>
       </c>
       <c r="H214" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>243</v>
       </c>
@@ -8196,10 +8207,10 @@
         <v>446</v>
       </c>
       <c r="H215" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>244</v>
       </c>
@@ -8219,10 +8230,10 @@
         <v>446</v>
       </c>
       <c r="H216" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>245</v>
       </c>
@@ -8242,10 +8253,10 @@
         <v>446</v>
       </c>
       <c r="H217" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>246</v>
       </c>
@@ -8265,10 +8276,10 @@
         <v>446</v>
       </c>
       <c r="H218" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>247</v>
       </c>
@@ -8288,10 +8299,10 @@
         <v>446</v>
       </c>
       <c r="H219" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>248</v>
       </c>
@@ -8311,10 +8322,10 @@
         <v>446</v>
       </c>
       <c r="H220" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>249</v>
       </c>
@@ -8334,10 +8345,10 @@
         <v>446</v>
       </c>
       <c r="H221" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>250</v>
       </c>
@@ -8357,10 +8368,10 @@
         <v>446</v>
       </c>
       <c r="H222" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>251</v>
       </c>
@@ -8380,10 +8391,10 @@
         <v>446</v>
       </c>
       <c r="H223" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>252</v>
       </c>
@@ -8403,10 +8414,10 @@
         <v>446</v>
       </c>
       <c r="H224" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>253</v>
       </c>
@@ -8426,10 +8437,10 @@
         <v>446</v>
       </c>
       <c r="H225" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>254</v>
       </c>
@@ -8449,10 +8460,10 @@
         <v>446</v>
       </c>
       <c r="H226" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -8475,7 +8486,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>256</v>
       </c>
@@ -8495,10 +8506,10 @@
         <v>446</v>
       </c>
       <c r="H228" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>257</v>
       </c>
@@ -8518,10 +8529,10 @@
         <v>446</v>
       </c>
       <c r="H229" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>258</v>
       </c>
@@ -8541,10 +8552,10 @@
         <v>446</v>
       </c>
       <c r="H230" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>259</v>
       </c>
@@ -8564,10 +8575,10 @@
         <v>446</v>
       </c>
       <c r="H231" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>260</v>
       </c>
@@ -8587,10 +8598,10 @@
         <v>446</v>
       </c>
       <c r="H232" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>261</v>
       </c>
@@ -8610,10 +8621,10 @@
         <v>446</v>
       </c>
       <c r="H233" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>262</v>
       </c>
@@ -8633,10 +8644,10 @@
         <v>446</v>
       </c>
       <c r="H234" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>263</v>
       </c>
@@ -8656,10 +8667,10 @@
         <v>446</v>
       </c>
       <c r="H235" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>264</v>
       </c>
@@ -8679,10 +8690,10 @@
         <v>446</v>
       </c>
       <c r="H236" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>265</v>
       </c>
@@ -8702,10 +8713,10 @@
         <v>446</v>
       </c>
       <c r="H237" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>266</v>
       </c>
@@ -8722,10 +8733,10 @@
         <v>446</v>
       </c>
       <c r="H238" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>267</v>
       </c>
@@ -8745,10 +8756,10 @@
         <v>446</v>
       </c>
       <c r="H239" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>268</v>
       </c>
@@ -8768,10 +8779,10 @@
         <v>446</v>
       </c>
       <c r="H240" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>269</v>
       </c>
@@ -8791,10 +8802,10 @@
         <v>446</v>
       </c>
       <c r="H241" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>270</v>
       </c>
@@ -8814,10 +8825,10 @@
         <v>446</v>
       </c>
       <c r="H242" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>271</v>
       </c>
@@ -8837,10 +8848,10 @@
         <v>446</v>
       </c>
       <c r="H243" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>272</v>
       </c>
@@ -8860,10 +8871,10 @@
         <v>452</v>
       </c>
       <c r="H244" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>273</v>
       </c>
@@ -8886,10 +8897,10 @@
         <v>452</v>
       </c>
       <c r="H245" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>274</v>
       </c>
@@ -8912,10 +8923,10 @@
         <v>452</v>
       </c>
       <c r="H246" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>275</v>
       </c>
@@ -8938,10 +8949,10 @@
         <v>452</v>
       </c>
       <c r="H247" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>276</v>
       </c>
@@ -8964,10 +8975,10 @@
         <v>452</v>
       </c>
       <c r="H248" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>277</v>
       </c>
@@ -8990,10 +9001,10 @@
         <v>452</v>
       </c>
       <c r="H249" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>278</v>
       </c>
@@ -9016,10 +9027,10 @@
         <v>452</v>
       </c>
       <c r="H250" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>279</v>
       </c>
@@ -9042,10 +9053,10 @@
         <v>452</v>
       </c>
       <c r="H251" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>280</v>
       </c>
@@ -9068,10 +9079,10 @@
         <v>452</v>
       </c>
       <c r="H252" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>281</v>
       </c>
@@ -9094,10 +9105,10 @@
         <v>452</v>
       </c>
       <c r="H253" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>282</v>
       </c>
@@ -9117,10 +9128,10 @@
         <v>452</v>
       </c>
       <c r="H254" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>283</v>
       </c>
@@ -9140,10 +9151,10 @@
         <v>452</v>
       </c>
       <c r="H255" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>284</v>
       </c>
@@ -9163,10 +9174,10 @@
         <v>452</v>
       </c>
       <c r="H256" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>285</v>
       </c>
@@ -9183,10 +9194,10 @@
         <v>446</v>
       </c>
       <c r="H257" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>286</v>
       </c>
@@ -9206,10 +9217,10 @@
         <v>446</v>
       </c>
       <c r="H258" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>287</v>
       </c>
@@ -9232,10 +9243,10 @@
         <v>446</v>
       </c>
       <c r="H259" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>288</v>
       </c>
@@ -9258,10 +9269,10 @@
         <v>446</v>
       </c>
       <c r="H260" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>289</v>
       </c>
@@ -9284,10 +9295,10 @@
         <v>446</v>
       </c>
       <c r="H261" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>290</v>
       </c>
@@ -9310,10 +9321,10 @@
         <v>446</v>
       </c>
       <c r="H262" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>291</v>
       </c>
@@ -9336,10 +9347,10 @@
         <v>446</v>
       </c>
       <c r="H263" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>292</v>
       </c>
@@ -9359,7 +9370,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>293</v>
       </c>
@@ -9376,10 +9387,10 @@
         <v>452</v>
       </c>
       <c r="H265" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>294</v>
       </c>
@@ -9399,7 +9410,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>295</v>
       </c>
@@ -9419,7 +9430,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>296</v>
       </c>
@@ -9436,10 +9447,10 @@
         <v>928</v>
       </c>
       <c r="H268" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>297</v>
       </c>
@@ -9456,10 +9467,10 @@
         <v>928</v>
       </c>
       <c r="H269" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>298</v>
       </c>
@@ -9479,7 +9490,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>299</v>
       </c>
@@ -9499,7 +9510,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>300</v>
       </c>
@@ -9519,7 +9530,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>301</v>
       </c>
@@ -9536,10 +9547,10 @@
         <v>928</v>
       </c>
       <c r="H273" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>302</v>
       </c>
@@ -9556,10 +9567,10 @@
         <v>452</v>
       </c>
       <c r="H274" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>303</v>
       </c>
@@ -9576,10 +9587,10 @@
         <v>928</v>
       </c>
       <c r="H275" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>304</v>
       </c>
@@ -9602,7 +9613,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>305</v>
       </c>
@@ -9619,10 +9630,10 @@
         <v>928</v>
       </c>
       <c r="H277" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>306</v>
       </c>
@@ -9639,10 +9650,10 @@
         <v>446</v>
       </c>
       <c r="H278" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>307</v>
       </c>
@@ -9662,7 +9673,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>308</v>
       </c>
@@ -9679,10 +9690,10 @@
         <v>446</v>
       </c>
       <c r="H280" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>309</v>
       </c>
@@ -9699,10 +9710,10 @@
         <v>446</v>
       </c>
       <c r="H281" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>310</v>
       </c>
@@ -9719,10 +9730,10 @@
         <v>446</v>
       </c>
       <c r="H282" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>311</v>
       </c>
@@ -9739,10 +9750,10 @@
         <v>928</v>
       </c>
       <c r="H283" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>312</v>
       </c>
@@ -9759,10 +9770,10 @@
         <v>928</v>
       </c>
       <c r="H284" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>313</v>
       </c>
@@ -9779,10 +9790,10 @@
         <v>928</v>
       </c>
       <c r="H285" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>314</v>
       </c>
@@ -9799,10 +9810,10 @@
         <v>928</v>
       </c>
       <c r="H286" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>315</v>
       </c>
@@ -9819,10 +9830,10 @@
         <v>928</v>
       </c>
       <c r="H287" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>316</v>
       </c>
@@ -9839,10 +9850,10 @@
         <v>928</v>
       </c>
       <c r="H288" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>317</v>
       </c>
@@ -9859,10 +9870,10 @@
         <v>928</v>
       </c>
       <c r="H289" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>318</v>
       </c>
@@ -9879,10 +9890,10 @@
         <v>446</v>
       </c>
       <c r="H290" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>319</v>
       </c>
@@ -9899,10 +9910,10 @@
         <v>446</v>
       </c>
       <c r="H291" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>320</v>
       </c>
@@ -9925,7 +9936,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>530</v>
       </c>
@@ -9942,10 +9953,10 @@
         <v>928</v>
       </c>
       <c r="H293" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>531</v>
       </c>
@@ -9965,7 +9976,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>902</v>
       </c>
@@ -9982,10 +9993,10 @@
         <v>446</v>
       </c>
       <c r="H295" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>903</v>
       </c>
@@ -10002,10 +10013,10 @@
         <v>928</v>
       </c>
       <c r="H296" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>904</v>
       </c>
@@ -10022,10 +10033,10 @@
         <v>928</v>
       </c>
       <c r="H297" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>905</v>
       </c>
@@ -10042,10 +10053,10 @@
         <v>446</v>
       </c>
       <c r="H298" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>906</v>
       </c>
@@ -10062,10 +10073,10 @@
         <v>928</v>
       </c>
       <c r="H299" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>907</v>
       </c>
@@ -10082,12 +10093,26 @@
         <v>928</v>
       </c>
       <c r="H300" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G300" xr:uid="{5699022E-E034-4B52-8E71-081D69E78013}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;7&amp;K000000 In-Confidence</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d2b2326c-f811-4ccc-abcb-1b955c303c2e}" enabled="1" method="Standard" siteId="{dc781727-710e-4855-bc4c-690266a1b551}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>
--- a/WVS_Dataset/Codebook manual coded index.xlsx
+++ b/WVS_Dataset/Codebook manual coded index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Blob\Documents\GitHub\WorldView\WVS_Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\file\Usersj$\jwa349\Home\My Documents\GitHub\PSYC382_WVS7_Shiny\WVS_Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C2D07-F5F2-4F7E-92CC-8F053A43FFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A4E12E-FAB6-40F1-BD22-E964EB7A7A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5685" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{1F33E572-B13C-43FB-A92D-13F49A1A14C4}"/>
+    <workbookView xWindow="21440" yWindow="17150" windowWidth="21760" windowHeight="18860" xr2:uid="{1F33E572-B13C-43FB-A92D-13F49A1A14C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3239,18 +3239,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5699022E-E034-4B52-8E71-081D69E78013}">
   <dimension ref="A1:H300"/>
-  <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" customWidth="1"/>
-    <col min="3" max="3" width="70.5546875" customWidth="1"/>
-    <col min="4" max="5" width="16.21875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="27.109375" customWidth="1"/>
+    <col min="7" max="7" width="27.08984375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>922</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>932</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>923</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>196</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>197</v>
       </c>
@@ -7113,10 +7113,10 @@
         <v>928</v>
       </c>
       <c r="H169" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>198</v>
       </c>
@@ -7136,10 +7136,10 @@
         <v>928</v>
       </c>
       <c r="H170" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>200</v>
       </c>
@@ -7182,10 +7182,10 @@
         <v>928</v>
       </c>
       <c r="H172" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>201</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>202</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>203</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>204</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>205</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>206</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>207</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>208</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>209</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>210</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>211</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>212</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>213</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>214</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>215</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>216</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>217</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>218</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>219</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>220</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>221</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>222</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>223</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>224</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>225</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>226</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>227</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>228</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>229</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>230</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>231</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>232</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>233</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>234</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>235</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>236</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>237</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>238</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>239</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>240</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>241</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>242</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>243</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>244</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>245</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>246</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>247</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>248</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>249</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>250</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>251</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>252</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>253</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>254</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>255</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>256</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>257</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>258</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>259</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>260</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>261</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>262</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>263</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>264</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>265</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>266</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>267</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>268</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>269</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>270</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>271</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>272</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>273</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>274</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>275</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>276</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>277</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>278</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>279</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>280</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>281</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>282</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>283</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>284</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>285</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>286</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>287</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>288</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>289</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>290</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>291</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>292</v>
       </c>
@@ -9370,7 +9370,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>293</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>294</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>295</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>296</v>
       </c>
@@ -9450,7 +9450,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>297</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>298</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>299</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>300</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>301</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>302</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>303</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>304</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>305</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>306</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>307</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>308</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>309</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>310</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>311</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>312</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>313</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>314</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>315</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>316</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>317</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>318</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>319</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="292" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>320</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>530</v>
       </c>
@@ -9953,10 +9953,10 @@
         <v>928</v>
       </c>
       <c r="H293" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>531</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>902</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>903</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>904</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>905</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>906</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>907</v>
       </c>
